--- a/artfynd/A 56400-2020 artfynd.xlsx
+++ b/artfynd/A 56400-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56400-2020 artfynd.xlsx
+++ b/artfynd/A 56400-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>205590</v>
       </c>
       <c r="B2" t="n">
-        <v>100933</v>
+        <v>100935</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 56400-2020 artfynd.xlsx
+++ b/artfynd/A 56400-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,123 +790,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>207117</v>
-      </c>
-      <c r="B3" t="n">
-        <v>99331</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>693</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Färgginst</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Genista tinctoria</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Bygget, Fåleberg, Vg</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>437058.5582313457</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6515647.37078347</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Mariestad</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Hassle</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2010-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2010-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Funnen längs vägkanten på allmän väg.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Karin Arnell</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Karin Arnell</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
